--- a/product_selector_out/STM32F0 series.xlsx
+++ b/product_selector_out/STM32F0 series.xlsx
@@ -42,7 +42,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -74,6 +74,11 @@
         <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAD3"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -90,7 +95,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="bottom"/>
@@ -105,6 +110,7 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -18470,7 +18476,7 @@
       </c>
       <c r="AD65" s="4" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25, 27</t>
         </is>
       </c>
       <c r="AE65" s="4" t="inlineStr">
@@ -25925,109 +25931,109 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R13" s="9" t="inlineStr">
+      <c r="R13" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S13" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="T13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="U13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="V13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="W13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AB13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AC13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AD13" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AE13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH13" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AI13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ13" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AK13" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AL13" s="9" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S13" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="T13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="U13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="W13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AB13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AC13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AD13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AE13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AH13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AI13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AK13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AL13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AM13" s="8" t="inlineStr">
@@ -26252,109 +26258,109 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R14" s="9" t="inlineStr">
+      <c r="R14" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S14" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="T14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="U14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="V14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="W14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AB14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AC14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AD14" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AE14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH14" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AI14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ14" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AK14" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AL14" s="9" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S14" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="T14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="U14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="W14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AB14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AC14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AD14" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AE14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AH14" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AI14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ14" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AK14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AL14" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AM14" s="8" t="inlineStr">
@@ -26579,109 +26585,109 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R15" s="9" t="inlineStr">
+      <c r="R15" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="T15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="U15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="V15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="W15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AB15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AC15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AD15" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AE15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH15" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AI15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ15" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AK15" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AL15" s="9" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S15" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="T15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="U15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="W15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AB15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AC15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AD15" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AE15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AH15" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AI15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ15" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AK15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AL15" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AM15" s="8" t="inlineStr">
@@ -27887,109 +27893,109 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R19" s="9" t="inlineStr">
+      <c r="R19" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="T19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="U19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="V19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="W19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AB19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AC19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AD19" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AE19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH19" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AI19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ19" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AK19" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AL19" s="9" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S19" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="T19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="U19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="W19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AB19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AC19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AD19" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AE19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AH19" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AI19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ19" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AK19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AL19" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AM19" s="8" t="inlineStr">
@@ -29195,109 +29201,109 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R23" s="9" t="inlineStr">
+      <c r="R23" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S23" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="T23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="U23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="V23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="W23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AB23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AC23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AD23" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AE23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH23" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AI23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ23" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AK23" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AL23" s="9" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S23" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="T23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="U23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="W23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AB23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AC23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AD23" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AE23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AH23" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AI23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ23" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AK23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AL23" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AM23" s="8" t="inlineStr">
@@ -34754,14 +34760,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R40" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S40" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R40" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S40" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T40" s="6" t="inlineStr">
@@ -34849,14 +34855,14 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AK40" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AL40" s="7" t="inlineStr">
+      <c r="AK40" s="7" t="inlineStr">
         <is>
           <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AL40" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM40" s="8" t="inlineStr">
@@ -35735,14 +35741,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R43" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S43" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R43" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S43" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T43" s="6" t="inlineStr">
@@ -35830,14 +35836,14 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AK43" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AL43" s="7" t="inlineStr">
+      <c r="AK43" s="7" t="inlineStr">
         <is>
           <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AL43" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM43" s="8" t="inlineStr">
@@ -36062,14 +36068,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R44" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S44" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R44" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S44" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T44" s="6" t="inlineStr">
@@ -36157,14 +36163,14 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AK44" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AL44" s="7" t="inlineStr">
+      <c r="AK44" s="7" t="inlineStr">
         <is>
           <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AL44" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM44" s="8" t="inlineStr">
@@ -36389,14 +36395,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R45" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S45" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R45" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S45" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T45" s="6" t="inlineStr">
@@ -36484,14 +36490,14 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AK45" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AL45" s="7" t="inlineStr">
+      <c r="AK45" s="7" t="inlineStr">
         <is>
           <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AL45" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM45" s="8" t="inlineStr">
@@ -37370,14 +37376,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R48" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S48" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R48" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S48" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T48" s="6" t="inlineStr">
@@ -37465,14 +37471,14 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AK48" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AL48" s="7" t="inlineStr">
+      <c r="AK48" s="7" t="inlineStr">
         <is>
           <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AL48" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM48" s="8" t="inlineStr">
@@ -38024,14 +38030,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R50" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S50" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R50" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S50" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T50" s="6" t="inlineStr">
@@ -38119,14 +38125,14 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AK50" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AL50" s="7" t="inlineStr">
+      <c r="AK50" s="7" t="inlineStr">
         <is>
           <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AL50" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM50" s="8" t="inlineStr">
@@ -38678,14 +38684,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R52" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S52" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R52" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S52" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T52" s="6" t="inlineStr">
@@ -38768,19 +38774,19 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AJ52" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AK52" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AL52" s="7" t="inlineStr">
+      <c r="AJ52" s="7" t="inlineStr">
         <is>
           <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AK52" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AL52" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM52" s="8" t="inlineStr">
@@ -39005,14 +39011,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R53" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S53" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R53" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S53" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T53" s="6" t="inlineStr">
@@ -39095,19 +39101,19 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AJ53" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AK53" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AL53" s="7" t="inlineStr">
+      <c r="AJ53" s="7" t="inlineStr">
         <is>
           <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AK53" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AL53" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM53" s="8" t="inlineStr">
@@ -39332,14 +39338,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R54" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S54" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R54" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S54" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T54" s="6" t="inlineStr">
@@ -39427,14 +39433,14 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AK54" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AL54" s="7" t="inlineStr">
+      <c r="AK54" s="7" t="inlineStr">
         <is>
           <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AL54" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM54" s="8" t="inlineStr">
@@ -42602,109 +42608,109 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R64" s="9" t="inlineStr">
+      <c r="R64" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S64" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="T64" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="U64" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="V64" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="W64" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X64" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y64" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z64" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA64" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AB64" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AC64" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AD64" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AE64" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF64" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG64" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH64" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AI64" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ64" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AK64" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AL64" s="9" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S64" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="T64" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="U64" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V64" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="W64" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X64" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y64" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z64" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA64" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AB64" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AC64" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AD64" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AE64" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF64" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG64" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AH64" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AI64" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ64" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AK64" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AL64" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AM64" s="8" t="inlineStr">
@@ -42929,14 +42935,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R65" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S65" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R65" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S65" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T65" s="6" t="inlineStr">
@@ -42989,9 +42995,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AD65" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AD65" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AE65" s="8" t="inlineStr">
@@ -43024,14 +43030,14 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AK65" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AL65" s="7" t="inlineStr">
+      <c r="AK65" s="7" t="inlineStr">
         <is>
           <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AL65" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM65" s="8" t="inlineStr">
@@ -43583,14 +43589,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R67" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S67" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R67" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S67" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T67" s="6" t="inlineStr">
@@ -43643,9 +43649,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AD67" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AD67" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AE67" s="8" t="inlineStr">
@@ -43678,14 +43684,14 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AK67" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AL67" s="7" t="inlineStr">
+      <c r="AK67" s="7" t="inlineStr">
         <is>
           <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AL67" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM67" s="8" t="inlineStr">
@@ -44564,14 +44570,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R70" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S70" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R70" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S70" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T70" s="6" t="inlineStr">
@@ -44659,14 +44665,14 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AK70" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AL70" s="7" t="inlineStr">
+      <c r="AK70" s="7" t="inlineStr">
         <is>
           <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AL70" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM70" s="8" t="inlineStr">
@@ -44891,14 +44897,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R71" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S71" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R71" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S71" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T71" s="6" t="inlineStr">
@@ -44986,14 +44992,14 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AK71" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AL71" s="7" t="inlineStr">
+      <c r="AK71" s="7" t="inlineStr">
         <is>
           <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AL71" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM71" s="8" t="inlineStr">
@@ -45218,14 +45224,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R72" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S72" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R72" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S72" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T72" s="6" t="inlineStr">
@@ -45313,14 +45319,14 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AK72" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AL72" s="7" t="inlineStr">
+      <c r="AK72" s="7" t="inlineStr">
         <is>
           <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AL72" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM72" s="8" t="inlineStr">
@@ -45545,14 +45551,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R73" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S73" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R73" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S73" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T73" s="6" t="inlineStr">
@@ -45640,14 +45646,14 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AK73" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AL73" s="7" t="inlineStr">
+      <c r="AK73" s="7" t="inlineStr">
         <is>
           <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AL73" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM73" s="8" t="inlineStr">
@@ -47834,14 +47840,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R80" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S80" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R80" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S80" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T80" s="6" t="inlineStr">
@@ -47929,14 +47935,14 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AK80" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AL80" s="7" t="inlineStr">
+      <c r="AK80" s="7" t="inlineStr">
         <is>
           <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AL80" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM80" s="8" t="inlineStr">
@@ -48488,14 +48494,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R82" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S82" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R82" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S82" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T82" s="6" t="inlineStr">
@@ -48583,14 +48589,14 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AK82" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AL82" s="7" t="inlineStr">
+      <c r="AK82" s="7" t="inlineStr">
         <is>
           <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AL82" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM82" s="8" t="inlineStr">
@@ -49398,7 +49404,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D181"/>
+  <dimension ref="A1:D141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -49503,7 +49509,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -49513,19 +49519,19 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>summary row reads USART = 1 with no UART split; ST publishes USART and UART separately, so the cell's combined count answers neither column</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>STM32F038C6</t>
+          <t>STM32F038K6</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -49535,7 +49541,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32F038x6 family device features and peripheral counts lists UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
@@ -49547,7 +49553,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -49557,19 +49563,19 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Table 2. STM32F038x6 family device features and peripheral counts lists UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
+          <t>summary row reads USART = 1 with no UART split; ST publishes USART and UART separately, so the cell's combined count answers neither column</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STM32F038K6</t>
+          <t>STM32F038G6</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -49579,19 +49585,19 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32F038x6 family device features and peripheral counts lists UFQFPN28 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STM32F038K6</t>
+          <t>STM32F038G6</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -49601,19 +49607,19 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>summary row reads USART = 1 with no UART split; ST publishes USART and UART separately, so the cell's combined count answers neither column</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>STM32F038G6</t>
+          <t>STM32F098VC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -49623,19 +49629,19 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Table 2. STM32F038x6 family device features and peripheral counts lists UFQFPN28 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>STM32F038G6</t>
+          <t>STM32F098VC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -49645,19 +49651,19 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>STM32F038G6</t>
+          <t>STM32F048T6</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -49667,19 +49673,19 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>STM32F098VC</t>
+          <t>STM32F048T6</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -49696,12 +49702,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>STM32F098VC</t>
+          <t>STM32F098RC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -49718,12 +49724,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>STM32F048T6</t>
+          <t>STM32F098RC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -49740,12 +49746,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>STM32F048T6</t>
+          <t>STM32F038F6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -49755,19 +49761,19 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32F038x6 family device features and peripheral counts lists TSSOP20 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>STM32F098RC</t>
+          <t>STM32F038F6</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -49777,19 +49783,19 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>summary row reads USART = 1 with no UART split; ST publishes USART and UART separately, so the cell's combined count answers neither column</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>STM32F098RC</t>
+          <t>STM32F058C8</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -49806,12 +49812,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>STM32F038F6</t>
+          <t>STM32F058C8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -49821,14 +49827,14 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Table 2. STM32F038x6 family device features and peripheral counts lists TSSOP20 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>STM32F038F6</t>
+          <t>STM32F098CC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -49843,14 +49849,14 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>STM32F038F6</t>
+          <t>STM32F098CC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -49865,14 +49871,14 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>STM32F058C8</t>
+          <t>STM32F078CB</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -49894,7 +49900,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>STM32F058C8</t>
+          <t>STM32F078CB</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -49916,12 +49922,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>STM32F098CC</t>
+          <t>STM32F038E6</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -49931,19 +49937,19 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32F038x6 family device features and peripheral counts lists WLCSP25 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>STM32F098CC</t>
+          <t>STM32F038E6</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -49953,14 +49959,14 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>summary row reads USART = 1 with no UART split; ST publishes USART and UART separately, so the cell's combined count answers neither column</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>STM32F078CB</t>
+          <t>STM32F078RB</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -49982,7 +49988,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>STM32F078CB</t>
+          <t>STM32F078RB</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -50004,12 +50010,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>STM32F038E6</t>
+          <t>STM32F058R8</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -50019,19 +50025,19 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Table 2. STM32F038x6 family device features and peripheral counts lists WLCSP25 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>STM32F038E6</t>
+          <t>STM32F058R8</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -50041,19 +50047,19 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>STM32F038E6</t>
+          <t>STM32F048G6</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -50063,19 +50069,19 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>STM32F078RB</t>
+          <t>STM32F048G6</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -50092,12 +50098,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>STM32F078RB</t>
+          <t>STM32F078VB</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -50114,12 +50120,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>STM32F058R8</t>
+          <t>STM32F078VB</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -50136,12 +50142,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>STM32F058R8</t>
+          <t>STM32F048C6</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -50158,12 +50164,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>STM32F048G6</t>
+          <t>STM32F048C6</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -50180,12 +50186,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>STM32F048G6</t>
+          <t>STM32F030C8</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -50195,19 +50201,19 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>STM32F078VB</t>
+          <t>STM32F030C8</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -50217,19 +50223,19 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>STM32F078VB</t>
+          <t>STM32F030C8</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -50239,14 +50245,14 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 29. Switching output I/O current consumption</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>STM32F048C6</t>
+          <t>STM32F030R8</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -50261,14 +50267,14 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>STM32F048C6</t>
+          <t>STM32F030R8</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -50283,19 +50289,19 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>STM32F030C8</t>
+          <t>STM32F030R8</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -50305,19 +50311,19 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 29. Switching output I/O current consumption</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>STM32F030C8</t>
+          <t>STM32F030K6</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -50334,12 +50340,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>STM32F030C8</t>
+          <t>STM32F030K6</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -50349,19 +50355,19 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Table 29. Switching output I/O current consumption</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>STM32F030R8</t>
+          <t>STM32F030K6</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -50371,19 +50377,19 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 29. Switching output I/O current consumption</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>STM32F030R8</t>
+          <t>STM32F030C6</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -50400,12 +50406,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>STM32F030R8</t>
+          <t>STM32F030C6</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -50415,19 +50421,19 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Table 29. Switching output I/O current consumption</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>STM32F030K6</t>
+          <t>STM32F030C6</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -50437,19 +50443,19 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 29. Switching output I/O current consumption</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>STM32F030K6</t>
+          <t>STM32F030RC</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -50466,12 +50472,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>STM32F030K6</t>
+          <t>STM32F030RC</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -50481,19 +50487,19 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Table 29. Switching output I/O current consumption</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>STM32F030C6</t>
+          <t>STM32F030RC</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -50503,19 +50509,19 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 29. Switching output I/O current consumption</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>STM32F030C6</t>
+          <t>STM32F030F4</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -50532,12 +50538,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>STM32F030C6</t>
+          <t>STM32F030F4</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -50547,19 +50553,19 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Table 29. Switching output I/O current consumption</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>STM32F030RC</t>
+          <t>STM32F030F4</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -50569,19 +50575,19 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 29. Switching output I/O current consumption</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>STM32F030RC</t>
+          <t>STM32F070CB</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -50591,19 +50597,19 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>STM32F030RC</t>
+          <t>STM32F070CB</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -50613,19 +50619,19 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Table 29. Switching output I/O current consumption</t>
+          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>STM32F030F4</t>
+          <t>STM32F070CB</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -50635,19 +50641,19 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 27. Switching output I/O current consumption</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>STM32F030F4</t>
+          <t>STM32F070RB</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -50657,19 +50663,19 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>STM32F030F4</t>
+          <t>STM32F070RB</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -50679,19 +50685,19 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Table 29. Switching output I/O current consumption</t>
+          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>STM32F070CB</t>
+          <t>STM32F070RB</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -50701,19 +50707,19 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 27. Switching output I/O current consumption</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>STM32F070CB</t>
+          <t>STM32F030CC</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -50723,19 +50729,19 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>STM32F070CB</t>
+          <t>STM32F030CC</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -50745,19 +50751,19 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Table 27. Switching output I/O current consumption</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>STM32F070RB</t>
+          <t>STM32F030CC</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -50767,19 +50773,19 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 29. Switching output I/O current consumption</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>STM32F070RB</t>
+          <t>STM32F070F6</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -50796,12 +50802,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>STM32F070RB</t>
+          <t>STM32F070F6</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -50811,19 +50817,19 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Table 27. Switching output I/O current consumption</t>
+          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>STM32F030CC</t>
+          <t>STM32F070F6</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -50833,19 +50839,19 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 27. Switching output I/O current consumption</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>STM32F030CC</t>
+          <t>STM32F070C6</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -50855,19 +50861,19 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>STM32F030CC</t>
+          <t>STM32F070C6</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -50877,19 +50883,19 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Table 29. Switching output I/O current consumption</t>
+          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>STM32F070F6</t>
+          <t>STM32F070C6</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -50899,19 +50905,19 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 27. Switching output I/O current consumption</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>STM32F070F6</t>
+          <t>STM32F042G6</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -50921,19 +50927,19 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32F042x4/x6 device features and peripheral counts lists UQFPN28 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>STM32F070F6</t>
+          <t>STM32F072VB</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -50943,19 +50949,19 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Table 27. Switching output I/O current consumption</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>STM32F070C6</t>
+          <t>STM32F072VB</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -50965,19 +50971,19 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>STM32F070C6</t>
+          <t>STM32F072RB</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -50987,19 +50993,19 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>STM32F070C6</t>
+          <t>STM32F072RB</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -51009,14 +51015,14 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Table 27. Switching output I/O current consumption</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>STM32F042G6</t>
+          <t>STM32F042G4</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -51038,12 +51044,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>STM32F042G6</t>
+          <t>STM32F042K6</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -51053,19 +51059,19 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32F042x4/x6 device features and peripheral counts lists LQFP32, UQFPN32 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>STM32F042G6</t>
+          <t>STM32F042K4</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -51075,14 +51081,14 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32F042x4/x6 device features and peripheral counts lists LQFP32, UQFPN32 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>STM32F072VB</t>
+          <t>STM32F072R8</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -51104,7 +51110,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>STM32F072VB</t>
+          <t>STM32F072R8</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -51126,7 +51132,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>STM32F072RB</t>
+          <t>STM32F072C8</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -51148,7 +51154,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>STM32F072RB</t>
+          <t>STM32F072C8</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -51170,7 +51176,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>STM32F042G4</t>
+          <t>STM32F042F6</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -51185,14 +51191,14 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Table 2. STM32F042x4/x6 device features and peripheral counts lists UQFPN28 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32F042x4/x6 device features and peripheral counts lists TSSOP20 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>STM32F042G4</t>
+          <t>STM32F072CB</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -51214,7 +51220,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>STM32F042G4</t>
+          <t>STM32F072CB</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -51236,7 +51242,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>STM32F042K6</t>
+          <t>STM32F042F4</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -51251,14 +51257,14 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Table 2. STM32F042x4/x6 device features and peripheral counts lists LQFP32, UQFPN32 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32F042x4/x6 device features and peripheral counts lists TSSOP20 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>STM32F042K6</t>
+          <t>STM32F072V8</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -51280,7 +51286,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>STM32F042K6</t>
+          <t>STM32F072V8</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -51302,7 +51308,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>STM32F042K4</t>
+          <t>STM32F042C6</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -51317,19 +51323,19 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Table 2. STM32F042x4/x6 device features and peripheral counts lists LQFP32, UQFPN32 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32F042x4/x6 device features and peripheral counts lists LQFP48, UFQFPN48 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>STM32F042K4</t>
+          <t>STM32F042C4</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -51339,19 +51345,19 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32F042x4/x6 device features and peripheral counts lists LQFP48, UFQFPN48 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>STM32F042K4</t>
+          <t>STM32F042T6</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -51361,14 +51367,14 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32F042x4/x6 device features and peripheral counts lists WLCSP36 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>STM32F072R8</t>
+          <t>STM32F051R8</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -51390,7 +51396,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>STM32F072R8</t>
+          <t>STM32F051R8</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -51412,7 +51418,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>STM32F072C8</t>
+          <t>STM32F051C8</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -51434,7 +51440,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>STM32F072C8</t>
+          <t>STM32F051C8</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -51456,12 +51462,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>STM32F042F6</t>
+          <t>STM32F051R6</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -51471,19 +51477,19 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Table 2. STM32F042x4/x6 device features and peripheral counts lists TSSOP20 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>STM32F042F6</t>
+          <t>STM32F051R6</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -51500,12 +51506,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>STM32F042F6</t>
+          <t>STM32F091CC</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -51522,12 +51528,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>STM32F072CB</t>
+          <t>STM32F091CC</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -51544,12 +51550,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>STM32F072CB</t>
+          <t>STM32F071VB</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -51566,12 +51572,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>STM32F042F4</t>
+          <t>STM32F071VB</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -51581,14 +51587,14 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Table 2. STM32F042x4/x6 device features and peripheral counts lists TSSOP20 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>STM32F042F4</t>
+          <t>STM32F071RB</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -51610,7 +51616,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>STM32F042F4</t>
+          <t>STM32F071RB</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -51632,7 +51638,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>STM32F072V8</t>
+          <t>STM32F071V8</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -51654,7 +51660,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>STM32F072V8</t>
+          <t>STM32F071V8</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -51676,12 +51682,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>STM32F042C6</t>
+          <t>STM32F051K8</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -51691,19 +51697,19 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Table 2. STM32F042x4/x6 device features and peripheral counts lists LQFP48, UFQFPN48 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>STM32F042C6</t>
+          <t>STM32F051K8</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -51720,12 +51726,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>STM32F042C6</t>
+          <t>STM32F091VB</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -51742,12 +51748,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>STM32F042C4</t>
+          <t>STM32F091VB</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -51757,19 +51763,19 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Table 2. STM32F042x4/x6 device features and peripheral counts lists LQFP48, UFQFPN48 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>STM32F042C4</t>
+          <t>STM32F031E6</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -51779,19 +51785,19 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32F031x4/x6 family device features and peripheral counts lists WLCSP25 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>STM32F042C4</t>
+          <t>STM32F031E6</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -51801,14 +51807,14 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>summary row reads USART = 1 with no UART split; ST publishes USART and UART separately, so the cell's combined count answers neither column</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>STM32F042T6</t>
+          <t>STM32F031K4</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -51823,14 +51829,14 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Table 2. STM32F042x4/x6 device features and peripheral counts lists WLCSP36 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32F031x4/x6 family device features and peripheral counts lists LQFP32, UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>STM32F042T6</t>
+          <t>STM32F051C4</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -51852,7 +51858,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>STM32F042T6</t>
+          <t>STM32F051C4</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -51874,12 +51880,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>STM32F051R8</t>
+          <t>STM32F031K6</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -51889,19 +51895,19 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32F031x4/x6 family device features and peripheral counts lists LQFP32, UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>STM32F051R8</t>
+          <t>STM32F051R4</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -51918,12 +51924,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>STM32F051C8</t>
+          <t>STM32F051R4</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -51940,12 +51946,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>STM32F051C8</t>
+          <t>STM32F051K6</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -51962,12 +51968,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>STM32F051R6</t>
+          <t>STM32F051K6</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -51984,12 +51990,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>STM32F051R6</t>
+          <t>STM32F031F4</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -51999,19 +52005,19 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32F031x4/x6 family device features and peripheral counts lists TSSOP20 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>STM32F091CC</t>
+          <t>STM32F031F6</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -52021,19 +52027,19 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32F031x4/x6 family device features and peripheral counts lists TSSOP20 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>STM32F091CC</t>
+          <t>STM32F031G4</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -52043,19 +52049,19 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32F031x4/x6 family device features and peripheral counts lists UFQFPN28 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>STM32F071VB</t>
+          <t>STM32F031G6</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -52065,19 +52071,19 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32F031x4/x6 family device features and peripheral counts lists UFQFPN28 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>STM32F071VB</t>
+          <t>STM32F091VC</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -52094,12 +52100,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>STM32F071RB</t>
+          <t>STM32F091VC</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -52116,12 +52122,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>STM32F071RB</t>
+          <t>STM32F051C6</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -52138,12 +52144,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>STM32F071V8</t>
+          <t>STM32F051C6</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -52160,12 +52166,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>STM32F071V8</t>
+          <t>STM32F051T8</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -52182,12 +52188,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>STM32F051K8</t>
+          <t>STM32F051T8</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -52204,12 +52210,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>STM32F051K8</t>
+          <t>STM32F091RB</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -52226,12 +52232,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>STM32F091VB</t>
+          <t>STM32F091RB</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -52248,12 +52254,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>STM32F091VB</t>
+          <t>STM32F071C8</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -52270,12 +52276,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>STM32F031E6</t>
+          <t>STM32F071C8</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -52285,14 +52291,14 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Table 2. STM32F031x4/x6 family device features and peripheral counts lists WLCSP25 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>STM32F031E6</t>
+          <t>STM32F091RC</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -52307,14 +52313,14 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>STM32F031E6</t>
+          <t>STM32F091RC</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -52329,14 +52335,14 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>STM32F031K4</t>
+          <t>STM32F031C6</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -52351,14 +52357,14 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Table 2. STM32F031x4/x6 family device features and peripheral counts lists LQFP32, UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32F031x4/x6 family device features and peripheral counts lists LQFP48 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>STM32F031K4</t>
+          <t>STM32F051K4</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -52373,14 +52379,14 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>STM32F031K4</t>
+          <t>STM32F051K4</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -52395,19 +52401,19 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>STM32F051C4</t>
+          <t>STM32F031C4</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -52417,19 +52423,19 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32F031x4/x6 family device features and peripheral counts lists LQFP48 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>STM32F051C4</t>
+          <t>STM32F071CB</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -52446,12 +52452,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>STM32F031K6</t>
+          <t>STM32F071CB</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -52461,14 +52467,14 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Table 2. STM32F031x4/x6 family device features and peripheral counts lists LQFP32, UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>STM32F031K6</t>
+          <t>STM32F091CB</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -52483,14 +52489,14 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>STM32F031K6</t>
+          <t>STM32F091CB</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -52504,886 +52510,6 @@
         </is>
       </c>
       <c r="D141" t="inlineStr">
-        <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>STM32F051R4</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>STM32F051R4</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>STM32F051K6</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>STM32F051K6</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>STM32F031F4</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>Table 2. STM32F031x4/x6 family device features and peripheral counts lists TSSOP20 for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>STM32F031F4</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>STM32F031F4</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>STM32F031F6</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>Table 2. STM32F031x4/x6 family device features and peripheral counts lists TSSOP20 for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>STM32F031F6</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>STM32F031F6</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>STM32F031G4</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>Table 2. STM32F031x4/x6 family device features and peripheral counts lists UFQFPN28 for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>STM32F031G4</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>STM32F031G4</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>STM32F031G6</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>Table 2. STM32F031x4/x6 family device features and peripheral counts lists UFQFPN28 for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>STM32F031G6</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>STM32F031G6</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>STM32F091VC</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>STM32F091VC</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>STM32F051C6</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>STM32F051C6</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>STM32F051T8</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>STM32F051T8</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>STM32F091RB</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>STM32F091RB</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>STM32F071C8</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>STM32F071C8</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>STM32F091RC</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>STM32F091RC</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>STM32F031C6</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>Table 2. STM32F031x4/x6 family device features and peripheral counts lists LQFP48 for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>STM32F031C6</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>STM32F031C6</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>STM32F051K4</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>STM32F051K4</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>STM32F031C4</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>Table 2. STM32F031x4/x6 family device features and peripheral counts lists LQFP48 for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>STM32F031C4</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>STM32F031C4</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>STM32F071CB</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>STM32F071CB</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>STM32F091CB</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>STM32F091CB</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
         <is>
           <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>

--- a/product_selector_out/STM32F0 series.xlsx
+++ b/product_selector_out/STM32F0 series.xlsx
@@ -9168,7 +9168,7 @@
       </c>
       <c r="BM36" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32f070c6.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -33387,9 +33387,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E36" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F36" s="6" t="inlineStr">
@@ -33452,14 +33452,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R36" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S36" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S36" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="T36" s="6" t="inlineStr">
@@ -33607,19 +33607,19 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW36" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AX36" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY36" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AW36" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX36" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY36" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ36" s="6" t="inlineStr">
@@ -33687,9 +33687,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM36" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM36" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -49404,7 +49404,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D141"/>
+  <dimension ref="A1:D138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -50648,7 +50648,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>STM32F070RB</t>
+          <t>STM32F030CC</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -50663,14 +50663,14 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>STM32F070RB</t>
+          <t>STM32F030CC</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -50685,14 +50685,14 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>STM32F070RB</t>
+          <t>STM32F030CC</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -50707,14 +50707,14 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Table 27. Switching output I/O current consumption</t>
+          <t>Table 29. Switching output I/O current consumption</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>STM32F030CC</t>
+          <t>STM32F070F6</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -50729,14 +50729,14 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>STM32F030CC</t>
+          <t>STM32F070F6</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -50751,14 +50751,14 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>STM32F030CC</t>
+          <t>STM32F070F6</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -50773,14 +50773,14 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Table 29. Switching output I/O current consumption</t>
+          <t>Table 27. Switching output I/O current consumption</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>STM32F070F6</t>
+          <t>STM32F070C6</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -50802,7 +50802,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>STM32F070F6</t>
+          <t>STM32F070C6</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -50824,7 +50824,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>STM32F070F6</t>
+          <t>STM32F070C6</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -50846,12 +50846,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>STM32F070C6</t>
+          <t>STM32F042G6</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -50861,19 +50861,19 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32F042x4/x6 device features and peripheral counts lists UQFPN28 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>STM32F070C6</t>
+          <t>STM32F072VB</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -50883,19 +50883,19 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>STM32F070C6</t>
+          <t>STM32F072VB</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -50905,19 +50905,19 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Table 27. Switching output I/O current consumption</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>STM32F042G6</t>
+          <t>STM32F072RB</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -50927,19 +50927,19 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Table 2. STM32F042x4/x6 device features and peripheral counts lists UQFPN28 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>STM32F072VB</t>
+          <t>STM32F072RB</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -50956,12 +50956,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>STM32F072VB</t>
+          <t>STM32F042G4</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -50971,19 +50971,19 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32F042x4/x6 device features and peripheral counts lists UQFPN28 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>STM32F072RB</t>
+          <t>STM32F042K6</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -50993,19 +50993,19 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32F042x4/x6 device features and peripheral counts lists LQFP32, UQFPN32 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>STM32F072RB</t>
+          <t>STM32F042K4</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -51015,19 +51015,19 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32F042x4/x6 device features and peripheral counts lists LQFP32, UQFPN32 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>STM32F042G4</t>
+          <t>STM32F072R8</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -51037,19 +51037,19 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Table 2. STM32F042x4/x6 device features and peripheral counts lists UQFPN28 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>STM32F042K6</t>
+          <t>STM32F072R8</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -51059,19 +51059,19 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Table 2. STM32F042x4/x6 device features and peripheral counts lists LQFP32, UQFPN32 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>STM32F042K4</t>
+          <t>STM32F072C8</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -51081,19 +51081,19 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Table 2. STM32F042x4/x6 device features and peripheral counts lists LQFP32, UQFPN32 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>STM32F072R8</t>
+          <t>STM32F072C8</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -51110,12 +51110,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>STM32F072R8</t>
+          <t>STM32F042F6</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -51125,14 +51125,14 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32F042x4/x6 device features and peripheral counts lists TSSOP20 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>STM32F072C8</t>
+          <t>STM32F072CB</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -51154,7 +51154,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>STM32F072C8</t>
+          <t>STM32F072CB</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -51176,7 +51176,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>STM32F042F6</t>
+          <t>STM32F042F4</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -51198,7 +51198,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>STM32F072CB</t>
+          <t>STM32F072V8</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -51220,7 +51220,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>STM32F072CB</t>
+          <t>STM32F072V8</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -51242,7 +51242,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>STM32F042F4</t>
+          <t>STM32F042C6</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -51257,19 +51257,19 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Table 2. STM32F042x4/x6 device features and peripheral counts lists TSSOP20 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32F042x4/x6 device features and peripheral counts lists LQFP48, UFQFPN48 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>STM32F072V8</t>
+          <t>STM32F042C4</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -51279,19 +51279,19 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32F042x4/x6 device features and peripheral counts lists LQFP48, UFQFPN48 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>STM32F072V8</t>
+          <t>STM32F042T6</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -51301,19 +51301,19 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32F042x4/x6 device features and peripheral counts lists WLCSP36 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>STM32F042C6</t>
+          <t>STM32F051R8</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -51323,19 +51323,19 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Table 2. STM32F042x4/x6 device features and peripheral counts lists LQFP48, UFQFPN48 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>STM32F042C4</t>
+          <t>STM32F051R8</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -51345,19 +51345,19 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Table 2. STM32F042x4/x6 device features and peripheral counts lists LQFP48, UFQFPN48 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>STM32F042T6</t>
+          <t>STM32F051C8</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -51367,19 +51367,19 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Table 2. STM32F042x4/x6 device features and peripheral counts lists WLCSP36 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>STM32F051R8</t>
+          <t>STM32F051C8</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -51396,12 +51396,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>STM32F051R8</t>
+          <t>STM32F051R6</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -51418,12 +51418,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>STM32F051C8</t>
+          <t>STM32F051R6</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -51440,12 +51440,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>STM32F051C8</t>
+          <t>STM32F091CC</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -51462,12 +51462,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>STM32F051R6</t>
+          <t>STM32F091CC</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -51484,12 +51484,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>STM32F051R6</t>
+          <t>STM32F071VB</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -51506,12 +51506,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>STM32F091CC</t>
+          <t>STM32F071VB</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -51528,12 +51528,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>STM32F091CC</t>
+          <t>STM32F071RB</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -51550,12 +51550,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>STM32F071VB</t>
+          <t>STM32F071RB</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -51572,12 +51572,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>STM32F071VB</t>
+          <t>STM32F071V8</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -51594,12 +51594,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>STM32F071RB</t>
+          <t>STM32F071V8</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -51616,12 +51616,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>STM32F071RB</t>
+          <t>STM32F051K8</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -51638,12 +51638,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>STM32F071V8</t>
+          <t>STM32F051K8</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -51660,12 +51660,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>STM32F071V8</t>
+          <t>STM32F091VB</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -51682,12 +51682,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>STM32F051K8</t>
+          <t>STM32F091VB</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -51704,12 +51704,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>STM32F051K8</t>
+          <t>STM32F031E6</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -51719,19 +51719,19 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32F031x4/x6 family device features and peripheral counts lists WLCSP25 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>STM32F091VB</t>
+          <t>STM32F031E6</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -51741,19 +51741,19 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>summary row reads USART = 1 with no UART split; ST publishes USART and UART separately, so the cell's combined count answers neither column</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>STM32F091VB</t>
+          <t>STM32F031K4</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -51763,19 +51763,19 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32F031x4/x6 family device features and peripheral counts lists LQFP32, UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>STM32F031E6</t>
+          <t>STM32F051C4</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -51785,19 +51785,19 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Table 2. STM32F031x4/x6 family device features and peripheral counts lists WLCSP25 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>STM32F031E6</t>
+          <t>STM32F051C4</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -51807,14 +51807,14 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>summary row reads USART = 1 with no UART split; ST publishes USART and UART separately, so the cell's combined count answers neither column</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>STM32F031K4</t>
+          <t>STM32F031K6</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -51836,7 +51836,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>STM32F051C4</t>
+          <t>STM32F051R4</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -51858,7 +51858,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>STM32F051C4</t>
+          <t>STM32F051R4</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -51880,12 +51880,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>STM32F031K6</t>
+          <t>STM32F051K6</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -51895,19 +51895,19 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Table 2. STM32F031x4/x6 family device features and peripheral counts lists LQFP32, UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>STM32F051R4</t>
+          <t>STM32F051K6</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -51924,12 +51924,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>STM32F051R4</t>
+          <t>STM32F031F4</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -51939,19 +51939,19 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32F031x4/x6 family device features and peripheral counts lists TSSOP20 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>STM32F051K6</t>
+          <t>STM32F031F6</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -51961,19 +51961,19 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32F031x4/x6 family device features and peripheral counts lists TSSOP20 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>STM32F051K6</t>
+          <t>STM32F031G4</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -51983,14 +51983,14 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32F031x4/x6 family device features and peripheral counts lists UFQFPN28 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>STM32F031F4</t>
+          <t>STM32F031G6</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -52005,19 +52005,19 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Table 2. STM32F031x4/x6 family device features and peripheral counts lists TSSOP20 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32F031x4/x6 family device features and peripheral counts lists UFQFPN28 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>STM32F031F6</t>
+          <t>STM32F091VC</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -52027,19 +52027,19 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Table 2. STM32F031x4/x6 family device features and peripheral counts lists TSSOP20 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>STM32F031G4</t>
+          <t>STM32F091VC</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -52049,19 +52049,19 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Table 2. STM32F031x4/x6 family device features and peripheral counts lists UFQFPN28 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>STM32F031G6</t>
+          <t>STM32F051C6</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -52071,19 +52071,19 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Table 2. STM32F031x4/x6 family device features and peripheral counts lists UFQFPN28 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>STM32F091VC</t>
+          <t>STM32F051C6</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -52100,12 +52100,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>STM32F091VC</t>
+          <t>STM32F051T8</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -52122,12 +52122,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>STM32F051C6</t>
+          <t>STM32F051T8</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -52144,12 +52144,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>STM32F051C6</t>
+          <t>STM32F091RB</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -52166,12 +52166,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>STM32F051T8</t>
+          <t>STM32F091RB</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -52188,12 +52188,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>STM32F051T8</t>
+          <t>STM32F071C8</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -52210,12 +52210,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>STM32F091RB</t>
+          <t>STM32F071C8</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -52232,12 +52232,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>STM32F091RB</t>
+          <t>STM32F091RC</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -52254,12 +52254,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>STM32F071C8</t>
+          <t>STM32F091RC</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -52276,12 +52276,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>STM32F071C8</t>
+          <t>STM32F031C6</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -52291,14 +52291,14 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32F031x4/x6 family device features and peripheral counts lists LQFP48 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>STM32F091RC</t>
+          <t>STM32F051K4</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -52320,7 +52320,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>STM32F091RC</t>
+          <t>STM32F051K4</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -52342,7 +52342,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>STM32F031C6</t>
+          <t>STM32F031C4</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -52364,7 +52364,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>STM32F051K4</t>
+          <t>STM32F071CB</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -52386,7 +52386,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>STM32F051K4</t>
+          <t>STM32F071CB</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -52408,12 +52408,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>STM32F031C4</t>
+          <t>STM32F091CB</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -52423,19 +52423,19 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Table 2. STM32F031x4/x6 family device features and peripheral counts lists LQFP48 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>STM32F071CB</t>
+          <t>STM32F091CB</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -52444,72 +52444,6 @@
         </is>
       </c>
       <c r="D138" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>STM32F071CB</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>STM32F091CB</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>STM32F091CB</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
         <is>
           <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>

--- a/product_selector_out/STM32F0 series.xlsx
+++ b/product_selector_out/STM32F0 series.xlsx
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM84"/>
+  <dimension ref="A1:BN84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.4375" customWidth="1" min="1" max="1"/>
@@ -573,7 +573,8 @@
     <col width="21.765625" customWidth="1" min="62" max="62"/>
     <col width="18" customWidth="1" min="63" max="63"/>
     <col width="18" customWidth="1" min="64" max="64"/>
-    <col width="52" customWidth="1" min="65" max="65"/>
+    <col width="18" customWidth="1" min="65" max="65"/>
+    <col width="52" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -901,6 +902,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -996,6 +1002,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1320,6 +1327,11 @@
       </c>
       <c r="BM12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f058c8.pdf</t>
         </is>
       </c>
@@ -1647,6 +1659,11 @@
       </c>
       <c r="BM13" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN13" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f038c6.pdf</t>
         </is>
       </c>
@@ -1974,6 +1991,11 @@
       </c>
       <c r="BM14" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f038c6.pdf</t>
         </is>
       </c>
@@ -2301,6 +2323,11 @@
       </c>
       <c r="BM15" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f038c6.pdf</t>
         </is>
       </c>
@@ -2628,6 +2655,11 @@
       </c>
       <c r="BM16" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN16" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f098cc.pdf</t>
         </is>
       </c>
@@ -2955,6 +2987,11 @@
       </c>
       <c r="BM17" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN17" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f048c6.pdf</t>
         </is>
       </c>
@@ -3282,6 +3319,11 @@
       </c>
       <c r="BM18" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN18" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f098cc.pdf</t>
         </is>
       </c>
@@ -3609,6 +3651,11 @@
       </c>
       <c r="BM19" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN19" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f038c6.pdf</t>
         </is>
       </c>
@@ -3936,6 +3983,11 @@
       </c>
       <c r="BM20" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN20" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f058c8.pdf</t>
         </is>
       </c>
@@ -4263,6 +4315,11 @@
       </c>
       <c r="BM21" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN21" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f098cc.pdf</t>
         </is>
       </c>
@@ -4590,6 +4647,11 @@
       </c>
       <c r="BM22" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN22" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f078cb.pdf</t>
         </is>
       </c>
@@ -4917,6 +4979,11 @@
       </c>
       <c r="BM23" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN23" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f038c6.pdf</t>
         </is>
       </c>
@@ -5244,6 +5311,11 @@
       </c>
       <c r="BM24" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN24" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f078cb.pdf</t>
         </is>
       </c>
@@ -5571,6 +5643,11 @@
       </c>
       <c r="BM25" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN25" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f058c8.pdf</t>
         </is>
       </c>
@@ -5898,6 +5975,11 @@
       </c>
       <c r="BM26" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN26" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f048c6.pdf</t>
         </is>
       </c>
@@ -6225,6 +6307,11 @@
       </c>
       <c r="BM27" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN27" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f078cb.pdf</t>
         </is>
       </c>
@@ -6552,6 +6639,11 @@
       </c>
       <c r="BM28" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN28" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f048c6.pdf</t>
         </is>
       </c>
@@ -6879,6 +6971,11 @@
       </c>
       <c r="BM29" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN29" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f030c6.pdf</t>
         </is>
       </c>
@@ -7206,6 +7303,11 @@
       </c>
       <c r="BM30" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN30" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f030c6.pdf</t>
         </is>
       </c>
@@ -7533,6 +7635,11 @@
       </c>
       <c r="BM31" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN31" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f030c6.pdf</t>
         </is>
       </c>
@@ -7860,6 +7967,11 @@
       </c>
       <c r="BM32" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN32" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f030c6.pdf</t>
         </is>
       </c>
@@ -8187,6 +8299,11 @@
       </c>
       <c r="BM33" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN33" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f030c6.pdf</t>
         </is>
       </c>
@@ -8514,6 +8631,11 @@
       </c>
       <c r="BM34" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN34" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f030c6.pdf</t>
         </is>
       </c>
@@ -8841,6 +8963,11 @@
       </c>
       <c r="BM35" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN35" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f070c6.pdf</t>
         </is>
       </c>
@@ -9171,6 +9298,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BN36" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
@@ -9495,6 +9627,11 @@
       </c>
       <c r="BM37" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN37" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f030c6.pdf</t>
         </is>
       </c>
@@ -9822,6 +9959,11 @@
       </c>
       <c r="BM38" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN38" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f070c6.pdf</t>
         </is>
       </c>
@@ -10149,6 +10291,11 @@
       </c>
       <c r="BM39" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN39" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f070c6.pdf</t>
         </is>
       </c>
@@ -10476,6 +10623,11 @@
       </c>
       <c r="BM40" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN40" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f042c4.pdf</t>
         </is>
       </c>
@@ -10803,6 +10955,11 @@
       </c>
       <c r="BM41" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN41" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f072c8.pdf</t>
         </is>
       </c>
@@ -11130,6 +11287,11 @@
       </c>
       <c r="BM42" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN42" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f072c8.pdf</t>
         </is>
       </c>
@@ -11457,6 +11619,11 @@
       </c>
       <c r="BM43" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN43" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f042c4.pdf</t>
         </is>
       </c>
@@ -11784,6 +11951,11 @@
       </c>
       <c r="BM44" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN44" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f042c4.pdf</t>
         </is>
       </c>
@@ -12111,6 +12283,11 @@
       </c>
       <c r="BM45" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN45" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f042c4.pdf</t>
         </is>
       </c>
@@ -12438,6 +12615,11 @@
       </c>
       <c r="BM46" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN46" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f072c8.pdf</t>
         </is>
       </c>
@@ -12765,6 +12947,11 @@
       </c>
       <c r="BM47" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN47" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f072c8.pdf</t>
         </is>
       </c>
@@ -13092,6 +13279,11 @@
       </c>
       <c r="BM48" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN48" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f042c4.pdf</t>
         </is>
       </c>
@@ -13419,6 +13611,11 @@
       </c>
       <c r="BM49" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN49" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f072c8.pdf</t>
         </is>
       </c>
@@ -13746,6 +13943,11 @@
       </c>
       <c r="BM50" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN50" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f042c4.pdf</t>
         </is>
       </c>
@@ -14073,6 +14275,11 @@
       </c>
       <c r="BM51" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN51" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f072c8.pdf</t>
         </is>
       </c>
@@ -14400,6 +14607,11 @@
       </c>
       <c r="BM52" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN52" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f042c4.pdf</t>
         </is>
       </c>
@@ -14727,6 +14939,11 @@
       </c>
       <c r="BM53" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN53" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f042c4.pdf</t>
         </is>
       </c>
@@ -15054,6 +15271,11 @@
       </c>
       <c r="BM54" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN54" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f042c4.pdf</t>
         </is>
       </c>
@@ -15381,6 +15603,11 @@
       </c>
       <c r="BM55" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN55" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f051c4.pdf</t>
         </is>
       </c>
@@ -15708,6 +15935,11 @@
       </c>
       <c r="BM56" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN56" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f051c4.pdf</t>
         </is>
       </c>
@@ -16035,6 +16267,11 @@
       </c>
       <c r="BM57" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN57" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f051c4.pdf</t>
         </is>
       </c>
@@ -16362,6 +16599,11 @@
       </c>
       <c r="BM58" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN58" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f091cb.pdf</t>
         </is>
       </c>
@@ -16689,6 +16931,11 @@
       </c>
       <c r="BM59" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN59" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f071c8.pdf</t>
         </is>
       </c>
@@ -17016,6 +17263,11 @@
       </c>
       <c r="BM60" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN60" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f071c8.pdf</t>
         </is>
       </c>
@@ -17343,6 +17595,11 @@
       </c>
       <c r="BM61" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN61" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f071c8.pdf</t>
         </is>
       </c>
@@ -17670,6 +17927,11 @@
       </c>
       <c r="BM62" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN62" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f051c4.pdf</t>
         </is>
       </c>
@@ -17997,6 +18259,11 @@
       </c>
       <c r="BM63" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN63" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f091cb.pdf</t>
         </is>
       </c>
@@ -18324,6 +18591,11 @@
       </c>
       <c r="BM64" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN64" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f031c4.pdf</t>
         </is>
       </c>
@@ -18651,6 +18923,11 @@
       </c>
       <c r="BM65" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN65" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f031c4.pdf</t>
         </is>
       </c>
@@ -18978,6 +19255,11 @@
       </c>
       <c r="BM66" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN66" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f051c4.pdf</t>
         </is>
       </c>
@@ -19305,6 +19587,11 @@
       </c>
       <c r="BM67" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN67" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f031c4.pdf</t>
         </is>
       </c>
@@ -19632,6 +19919,11 @@
       </c>
       <c r="BM68" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN68" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f051c4.pdf</t>
         </is>
       </c>
@@ -19959,6 +20251,11 @@
       </c>
       <c r="BM69" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN69" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f051c4.pdf</t>
         </is>
       </c>
@@ -20286,6 +20583,11 @@
       </c>
       <c r="BM70" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN70" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f031c4.pdf</t>
         </is>
       </c>
@@ -20613,6 +20915,11 @@
       </c>
       <c r="BM71" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN71" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f031c4.pdf</t>
         </is>
       </c>
@@ -20940,6 +21247,11 @@
       </c>
       <c r="BM72" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN72" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f031c4.pdf</t>
         </is>
       </c>
@@ -21267,6 +21579,11 @@
       </c>
       <c r="BM73" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN73" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f031c4.pdf</t>
         </is>
       </c>
@@ -21594,6 +21911,11 @@
       </c>
       <c r="BM74" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN74" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f091cb.pdf</t>
         </is>
       </c>
@@ -21921,6 +22243,11 @@
       </c>
       <c r="BM75" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN75" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f051c4.pdf</t>
         </is>
       </c>
@@ -22248,6 +22575,11 @@
       </c>
       <c r="BM76" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN76" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f051c4.pdf</t>
         </is>
       </c>
@@ -22575,6 +22907,11 @@
       </c>
       <c r="BM77" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN77" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f091cb.pdf</t>
         </is>
       </c>
@@ -22902,6 +23239,11 @@
       </c>
       <c r="BM78" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN78" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f071c8.pdf</t>
         </is>
       </c>
@@ -23229,6 +23571,11 @@
       </c>
       <c r="BM79" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN79" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f091cb.pdf</t>
         </is>
       </c>
@@ -23556,6 +23903,11 @@
       </c>
       <c r="BM80" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN80" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f031c4.pdf</t>
         </is>
       </c>
@@ -23883,6 +24235,11 @@
       </c>
       <c r="BM81" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN81" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f051c4.pdf</t>
         </is>
       </c>
@@ -24210,6 +24567,11 @@
       </c>
       <c r="BM82" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN82" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f031c4.pdf</t>
         </is>
       </c>
@@ -24537,6 +24899,11 @@
       </c>
       <c r="BM83" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN83" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f071c8.pdf</t>
         </is>
       </c>
@@ -24864,12 +25231,17 @@
       </c>
       <c r="BM84" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN84" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f091cb.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="64">
+  <mergeCells count="65">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -24890,16 +25262,14 @@
     <mergeCell ref="BA10:BA11"/>
     <mergeCell ref="BG10:BG11"/>
     <mergeCell ref="Q10:Q11"/>
-    <mergeCell ref="A1:BM8"/>
     <mergeCell ref="AR10:AR11"/>
+    <mergeCell ref="AT10:AT11"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="AT10:AT11"/>
+    <mergeCell ref="BI10:BI11"/>
     <mergeCell ref="AV10:AV11"/>
-    <mergeCell ref="A9:BM9"/>
     <mergeCell ref="BB10:BB11"/>
-    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -24912,6 +25282,7 @@
     <mergeCell ref="AQ10:AQ11"/>
     <mergeCell ref="AW10:AW11"/>
     <mergeCell ref="BH10:BH11"/>
+    <mergeCell ref="BN10:BN11"/>
     <mergeCell ref="AY10:AY11"/>
     <mergeCell ref="BK10:BK11"/>
     <mergeCell ref="A10:A11"/>
@@ -24931,7 +25302,9 @@
     <mergeCell ref="U10:V10"/>
     <mergeCell ref="AG10:AG11"/>
     <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A9:BN9"/>
     <mergeCell ref="H10:H11"/>
+    <mergeCell ref="A1:BN8"/>
     <mergeCell ref="T10:T11"/>
     <mergeCell ref="J10:J11"/>
   </mergeCells>
@@ -25021,7 +25394,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM84"/>
+  <dimension ref="A1:BN84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -25089,6 +25462,7 @@
     <col width="16" customWidth="1" min="63" max="63"/>
     <col width="16" customWidth="1" min="64" max="64"/>
     <col width="16" customWidth="1" min="65" max="65"/>
+    <col width="16" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -25422,6 +25796,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -25517,6 +25896,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -25839,7 +26219,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM12" s="6" t="inlineStr">
+      <c r="BM12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -26166,7 +26551,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM13" s="6" t="inlineStr">
+      <c r="BM13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN13" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -26493,7 +26883,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM14" s="6" t="inlineStr">
+      <c r="BM14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -26820,7 +27215,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM15" s="6" t="inlineStr">
+      <c r="BM15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -27147,7 +27547,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM16" s="6" t="inlineStr">
+      <c r="BM16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN16" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -27474,7 +27879,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM17" s="6" t="inlineStr">
+      <c r="BM17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN17" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -27801,7 +28211,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM18" s="6" t="inlineStr">
+      <c r="BM18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN18" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -28128,7 +28543,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM19" s="6" t="inlineStr">
+      <c r="BM19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN19" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -28455,7 +28875,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM20" s="6" t="inlineStr">
+      <c r="BM20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN20" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -28782,7 +29207,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM21" s="6" t="inlineStr">
+      <c r="BM21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN21" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -29109,7 +29539,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM22" s="6" t="inlineStr">
+      <c r="BM22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN22" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -29436,7 +29871,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM23" s="6" t="inlineStr">
+      <c r="BM23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN23" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -29763,7 +30203,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM24" s="6" t="inlineStr">
+      <c r="BM24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN24" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -30090,7 +30535,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM25" s="6" t="inlineStr">
+      <c r="BM25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN25" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -30417,7 +30867,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM26" s="6" t="inlineStr">
+      <c r="BM26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN26" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -30744,7 +31199,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM27" s="6" t="inlineStr">
+      <c r="BM27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN27" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -31071,7 +31531,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM28" s="6" t="inlineStr">
+      <c r="BM28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN28" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -31398,7 +31863,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM29" s="6" t="inlineStr">
+      <c r="BM29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN29" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -31725,7 +32195,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM30" s="6" t="inlineStr">
+      <c r="BM30" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN30" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -32052,7 +32527,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM31" s="6" t="inlineStr">
+      <c r="BM31" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN31" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -32379,7 +32859,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM32" s="6" t="inlineStr">
+      <c r="BM32" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN32" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -32706,7 +33191,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM33" s="6" t="inlineStr">
+      <c r="BM33" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN33" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -33033,7 +33523,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM34" s="6" t="inlineStr">
+      <c r="BM34" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN34" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -33360,7 +33855,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM35" s="6" t="inlineStr">
+      <c r="BM35" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN35" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -33692,6 +34192,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BN36" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
@@ -34014,7 +34519,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM37" s="6" t="inlineStr">
+      <c r="BM37" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN37" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -34341,7 +34851,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM38" s="6" t="inlineStr">
+      <c r="BM38" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN38" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -34668,7 +35183,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM39" s="6" t="inlineStr">
+      <c r="BM39" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN39" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -34995,7 +35515,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM40" s="6" t="inlineStr">
+      <c r="BM40" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN40" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -35322,7 +35847,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM41" s="6" t="inlineStr">
+      <c r="BM41" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN41" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -35649,7 +36179,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM42" s="6" t="inlineStr">
+      <c r="BM42" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN42" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -35976,7 +36511,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM43" s="6" t="inlineStr">
+      <c r="BM43" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN43" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -36303,7 +36843,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM44" s="6" t="inlineStr">
+      <c r="BM44" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN44" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -36630,7 +37175,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM45" s="6" t="inlineStr">
+      <c r="BM45" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN45" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -36957,7 +37507,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM46" s="6" t="inlineStr">
+      <c r="BM46" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN46" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -37284,7 +37839,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM47" s="6" t="inlineStr">
+      <c r="BM47" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN47" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -37611,7 +38171,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM48" s="6" t="inlineStr">
+      <c r="BM48" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN48" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -37938,7 +38503,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM49" s="6" t="inlineStr">
+      <c r="BM49" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN49" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -38265,7 +38835,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM50" s="6" t="inlineStr">
+      <c r="BM50" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN50" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -38592,7 +39167,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM51" s="6" t="inlineStr">
+      <c r="BM51" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN51" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -38919,7 +39499,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM52" s="6" t="inlineStr">
+      <c r="BM52" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN52" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -39246,7 +39831,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM53" s="6" t="inlineStr">
+      <c r="BM53" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN53" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -39573,7 +40163,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM54" s="6" t="inlineStr">
+      <c r="BM54" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN54" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -39900,7 +40495,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM55" s="6" t="inlineStr">
+      <c r="BM55" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN55" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -40227,7 +40827,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM56" s="6" t="inlineStr">
+      <c r="BM56" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN56" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -40554,7 +41159,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM57" s="6" t="inlineStr">
+      <c r="BM57" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN57" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -40881,7 +41491,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM58" s="6" t="inlineStr">
+      <c r="BM58" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN58" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -41208,7 +41823,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM59" s="6" t="inlineStr">
+      <c r="BM59" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN59" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -41535,7 +42155,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM60" s="6" t="inlineStr">
+      <c r="BM60" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN60" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -41862,7 +42487,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM61" s="6" t="inlineStr">
+      <c r="BM61" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN61" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -42189,7 +42819,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM62" s="6" t="inlineStr">
+      <c r="BM62" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN62" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -42516,7 +43151,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM63" s="6" t="inlineStr">
+      <c r="BM63" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN63" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -42843,7 +43483,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM64" s="6" t="inlineStr">
+      <c r="BM64" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN64" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -43170,7 +43815,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM65" s="6" t="inlineStr">
+      <c r="BM65" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN65" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -43497,7 +44147,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM66" s="6" t="inlineStr">
+      <c r="BM66" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN66" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -43824,7 +44479,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM67" s="6" t="inlineStr">
+      <c r="BM67" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN67" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -44151,7 +44811,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM68" s="6" t="inlineStr">
+      <c r="BM68" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN68" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -44478,7 +45143,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM69" s="6" t="inlineStr">
+      <c r="BM69" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN69" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -44805,7 +45475,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM70" s="6" t="inlineStr">
+      <c r="BM70" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN70" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -45132,7 +45807,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM71" s="6" t="inlineStr">
+      <c r="BM71" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN71" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -45459,7 +46139,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM72" s="6" t="inlineStr">
+      <c r="BM72" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN72" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -45786,7 +46471,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM73" s="6" t="inlineStr">
+      <c r="BM73" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN73" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -46113,7 +46803,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM74" s="6" t="inlineStr">
+      <c r="BM74" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN74" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -46440,7 +47135,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM75" s="6" t="inlineStr">
+      <c r="BM75" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN75" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -46767,7 +47467,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM76" s="6" t="inlineStr">
+      <c r="BM76" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN76" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -47094,7 +47799,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM77" s="6" t="inlineStr">
+      <c r="BM77" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN77" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -47421,7 +48131,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM78" s="6" t="inlineStr">
+      <c r="BM78" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN78" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -47748,7 +48463,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM79" s="6" t="inlineStr">
+      <c r="BM79" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN79" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -48075,7 +48795,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM80" s="6" t="inlineStr">
+      <c r="BM80" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN80" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -48402,7 +49127,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM81" s="6" t="inlineStr">
+      <c r="BM81" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN81" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -48729,7 +49459,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM82" s="6" t="inlineStr">
+      <c r="BM82" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN82" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -49056,7 +49791,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM83" s="6" t="inlineStr">
+      <c r="BM83" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN83" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -49383,7 +50123,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM84" s="6" t="inlineStr">
+      <c r="BM84" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN84" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -49391,8 +50136,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:BM9"/>
-    <mergeCell ref="A1:BM8"/>
+    <mergeCell ref="A9:BN9"/>
+    <mergeCell ref="A1:BN8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
